--- a/jpcore-r4b/develop/CodeSystem-jp-undefined-cs.xlsx
+++ b/jpcore-r4b/develop/CodeSystem-jp-undefined-cs.xlsx
@@ -71,7 +71,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/CodeSystem-jp-undefined-cs.xlsx
+++ b/jpcore-r4b/develop/CodeSystem-jp-undefined-cs.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -92,7 +92,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
@@ -116,7 +116,7 @@
     <t>Content</t>
   </si>
   <si>
-    <t>complete</t>
+    <t>fragment</t>
   </si>
   <si>
     <t>Supplements</t>

--- a/jpcore-r4b/develop/CodeSystem-jp-undefined-cs.xlsx
+++ b/jpcore-r4b/develop/CodeSystem-jp-undefined-cs.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>
